--- a/Chapt5Challenge.xlsx
+++ b/Chapt5Challenge.xlsx
@@ -8,14 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shareen\Desktop\GET A JOB\LearnExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A0DB36-4C3F-468B-954B-B1FAF61E35FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{657041D3-2385-495F-8F04-8227E21297C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{5344C77C-132B-45DC-AC0C-B651EB5E5F81}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="701" activeTab="5" xr2:uid="{5344C77C-132B-45DC-AC0C-B651EB5E5F81}"/>
   </bookViews>
   <sheets>
     <sheet name="SchoolShopping" sheetId="1" r:id="rId1"/>
     <sheet name="Humane Society Pets Adoption" sheetId="4" r:id="rId2"/>
     <sheet name="3vacations" sheetId="5" r:id="rId3"/>
+    <sheet name="printerCost" sheetId="6" r:id="rId4"/>
+    <sheet name="phone bill" sheetId="7" r:id="rId5"/>
+    <sheet name="Sheet3" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="114">
   <si>
     <t>Item</t>
   </si>
@@ -225,6 +228,162 @@
   <si>
     <t>Days</t>
   </si>
+  <si>
+    <t>Epsilon</t>
+  </si>
+  <si>
+    <t>Heavy Package</t>
+  </si>
+  <si>
+    <t>Zero</t>
+  </si>
+  <si>
+    <t>Prices</t>
+  </si>
+  <si>
+    <t>Cost of Catridges</t>
+  </si>
+  <si>
+    <t>Pages Cart. Can Print</t>
+  </si>
+  <si>
+    <t>Cost per Pages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expected pages </t>
+  </si>
+  <si>
+    <t>Days in a Week</t>
+  </si>
+  <si>
+    <t>Week in a Year</t>
+  </si>
+  <si>
+    <t>Total Pages in a Year</t>
+  </si>
+  <si>
+    <t>Pages per Year</t>
+  </si>
+  <si>
+    <t>Printing Cost per Year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Years </t>
+  </si>
+  <si>
+    <t>Total Printing Cost</t>
+  </si>
+  <si>
+    <t>monthly Subs</t>
+  </si>
+  <si>
+    <t>X-Mobile</t>
+  </si>
+  <si>
+    <t>Veritium</t>
+  </si>
+  <si>
+    <t>ABC</t>
+  </si>
+  <si>
+    <t>Data Limit (GB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phone rental </t>
+  </si>
+  <si>
+    <t>Extra Data charge</t>
+  </si>
+  <si>
+    <t>Susan phone rental option</t>
+  </si>
+  <si>
+    <t>total Month usaged</t>
+  </si>
+  <si>
+    <t>phone rental monthly use</t>
+  </si>
+  <si>
+    <t>phone intial cost</t>
+  </si>
+  <si>
+    <t>Total Cost</t>
+  </si>
+  <si>
+    <t>Tim phone rental option</t>
+  </si>
+  <si>
+    <t>extra usage (GB)</t>
+  </si>
+  <si>
+    <t>Total price</t>
+  </si>
+  <si>
+    <t>Chevy Spark</t>
+  </si>
+  <si>
+    <t>Ford Mustang</t>
+  </si>
+  <si>
+    <t>Cadillac Escalade</t>
+  </si>
+  <si>
+    <t>HP Engine</t>
+  </si>
+  <si>
+    <t>insurance ( yearly)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sales Tax </t>
+  </si>
+  <si>
+    <t xml:space="preserve">License </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Milleage </t>
+  </si>
+  <si>
+    <t>Yearly cost</t>
+  </si>
+  <si>
+    <t>Gas</t>
+  </si>
+  <si>
+    <t>Price per Gal Gas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Annual Gas </t>
+  </si>
+  <si>
+    <t>MPG (Miles per Gal)</t>
+  </si>
+  <si>
+    <t>the price per gallon is from california average price in July 2026</t>
+  </si>
+  <si>
+    <t>Annual Milleage</t>
+  </si>
+  <si>
+    <t>Lifepsan (Year)</t>
+  </si>
+  <si>
+    <t>Initial Cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Initial price </t>
+  </si>
+  <si>
+    <t>Loan</t>
+  </si>
+  <si>
+    <t>Interest Percentage</t>
+  </si>
+  <si>
+    <t>Interest amount</t>
+  </si>
+  <si>
+    <t>Milleage</t>
+  </si>
 </sst>
 </file>
 
@@ -233,7 +392,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -254,8 +413,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -304,6 +470,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -314,11 +498,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
@@ -335,19 +520,38 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="44" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="7" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="5">
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -365,9 +569,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
       <font>
@@ -841,6 +1042,294 @@
         </a:p>
       </c:txPr>
     </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$A$63</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet3!$B$62:$D$62</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Chevy Spark</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Ford Mustang</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Cadillac Escalade</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$B$63:$D$63</c:f>
+              <c:numCache>
+                <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>74214.28571428571</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>140228.0701754386</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>216259.80392156861</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C02A-4B9D-8D20-02FBE7F90A3C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1509026303"/>
+        <c:axId val="1509026783"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1509026303"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1509026783"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1509026783"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1509026303"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -1913,7 +2402,1661 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Susans Printing</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>printerCost!$A$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>printerCost!$B$19:$D$19</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Epsilon</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Heavy Package</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Zero</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>printerCost!$B$20:$D$20</c:f>
+              <c:numCache>
+                <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>1589</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>851</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>811.36363636363637</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5B1F-4385-AB0B-6880080859C1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1313191999"/>
+        <c:axId val="1313192959"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1313191999"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1313192959"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1313192959"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1313191999"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Tim's Printing</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>printerCost!$A$41</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>printerCost!$B$40:$D$40</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Epsilon</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Heavy Package</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Zero</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>printerCost!$B$41:$D$41</c:f>
+              <c:numCache>
+                <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>52029</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>23549</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9294.454545454546</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-98E5-4CD4-9F31-975D1E0C2DC7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1509002303"/>
+        <c:axId val="1509003263"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1509002303"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1509003263"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1509003263"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1509002303"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+              <a:lnSpc>
+                <a:spcPct val="100000"/>
+              </a:lnSpc>
+              <a:spcBef>
+                <a:spcPts val="0"/>
+              </a:spcBef>
+              <a:spcAft>
+                <a:spcPts val="0"/>
+              </a:spcAft>
+              <a:buClrTx/>
+              <a:buSzTx/>
+              <a:buFontTx/>
+              <a:buNone/>
+              <a:tabLst/>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Susan 2 year plan Cell phone bill</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'phone bill'!$A$17</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'phone bill'!$B$16:$D$16</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>X-Mobile</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Veritium</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>ABC</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'phone bill'!$B$17:$D$17</c:f>
+              <c:numCache>
+                <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>2136</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2060</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1560</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7174-4927-96B1-65D4B2883AEF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="1509015743"/>
+        <c:axId val="1509023903"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1509015743"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1509023903"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1509023903"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1509015743"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Tims 2</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> year plan Cell phone bill</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'phone bill'!$A$35</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'phone bill'!$B$34:$D$34</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>X-Mobile</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Veritium</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>ABC</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'phone bill'!$B$35:$D$35</c:f>
+              <c:numCache>
+                <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>1176</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1340</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1320</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FC13-40A0-BE0F-062C17F9B4EB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1508979743"/>
+        <c:axId val="1508977343"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1508979743"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1508977343"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1508977343"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1508979743"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l">
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Susans option</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>total cost</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> of getting a car</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.24797900262467193"/>
+          <c:y val="5.5555555555555552E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l">
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet3!$B$30:$D$30</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Chevy Spark</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Ford Mustang</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Cadillac Escalade</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$B$31:$D$31</c:f>
+              <c:numCache>
+                <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>68414.28571428571</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>127828.07017543861</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>187459.80392156861</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7D33-448A-851C-99FDFF29984D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1509014783"/>
+        <c:axId val="1509007103"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1509014783"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1509007103"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1509007103"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1509014783"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors10.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -2073,6 +4216,206 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="286">
   <cs:axisTitle>
@@ -2567,7 +4910,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style10.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -3070,8 +5413,8 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -3275,6 +5618,509 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
@@ -3576,6 +6422,2523 @@
 </file>
 
 <file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -4237,19 +9600,250 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>409575</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>23812</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>100012</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67E9B514-52E4-50F2-E6FB-20E04FA4E99C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>466725</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>71437</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>147637</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2888B60D-9DB6-6C3A-0E3E-BFF5295989F3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>128587</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>14287</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC5B14A9-AF5B-75FB-8244-40E250232433}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>80962</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>166687</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>385762</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>52387</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B8E75AF-4751-66A2-5B8F-1697FD8FD3D6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>450849</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>146049</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D840BFEB-9A75-44F0-0B81-1A97D7983FEB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>476249</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>171449</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40AAB4E3-1B2C-55F9-77D5-F97AEBEDD1F8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{66A7AEC2-C942-4F56-911D-94589DC87895}" name="Table1" displayName="Table1" ref="A2:E4" totalsRowShown="0" dataDxfId="0" dataCellStyle="Currency">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{66A7AEC2-C942-4F56-911D-94589DC87895}" name="Table1" displayName="Table1" ref="A2:E4" totalsRowShown="0" dataDxfId="4" dataCellStyle="Currency">
   <autoFilter ref="A2:E4" xr:uid="{66A7AEC2-C942-4F56-911D-94589DC87895}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{4CB64636-CA19-437F-B06E-6D4DEB088CD3}" name="Pets"/>
-    <tableColumn id="2" xr3:uid="{19192E72-3452-4C38-8C63-DE99A5D32BC3}" name="adoption fee" dataDxfId="4" dataCellStyle="Currency"/>
-    <tableColumn id="3" xr3:uid="{2FEEB945-89B3-4A68-B9D0-9C1A9CC7BAF3}" name="Accessory" dataDxfId="3" dataCellStyle="Currency">
+    <tableColumn id="2" xr3:uid="{19192E72-3452-4C38-8C63-DE99A5D32BC3}" name="adoption fee" dataDxfId="3" dataCellStyle="Currency"/>
+    <tableColumn id="3" xr3:uid="{2FEEB945-89B3-4A68-B9D0-9C1A9CC7BAF3}" name="Accessory" dataDxfId="2" dataCellStyle="Currency">
       <calculatedColumnFormula>2.5+5.5+7+3</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{466A5671-F15F-42B0-B461-A8691A0971B4}" name="Supplies (1 Year)" dataDxfId="2" dataCellStyle="Currency">
+    <tableColumn id="4" xr3:uid="{466A5671-F15F-42B0-B461-A8691A0971B4}" name="Supplies (1 Year)" dataDxfId="1" dataCellStyle="Currency">
       <calculatedColumnFormula>(21+3)*12</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{924AB36C-4334-4DCF-B731-C06328305927}" name="Total" dataDxfId="1">
+    <tableColumn id="5" xr3:uid="{924AB36C-4334-4DCF-B731-C06328305927}" name="Total" dataDxfId="0">
       <calculatedColumnFormula>SUM(B3:D3)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5463,8 +11057,8 @@
     <col min="4" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:4" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
         <v>45</v>
       </c>
     </row>
@@ -5612,13 +11206,13 @@
       <c r="A12" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="16">
         <v>2</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="16">
         <v>2</v>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="16">
         <v>2</v>
       </c>
     </row>
@@ -5626,15 +11220,15 @@
       <c r="A13" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="18">
+      <c r="B13" s="4">
         <f>(SUM(B3:B11) *B12)</f>
         <v>1100</v>
       </c>
-      <c r="C13" s="18">
+      <c r="C13" s="4">
         <f t="shared" ref="C13:D13" si="0">(SUM(C3:C11) *C12)</f>
         <v>728</v>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="4">
         <f t="shared" si="0"/>
         <v>134</v>
       </c>
@@ -5679,23 +11273,23 @@
       <c r="A18" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B18" s="19">
+      <c r="B18" s="17">
         <f>B16*B17</f>
         <v>700</v>
       </c>
-      <c r="C18" s="19">
+      <c r="C18" s="17">
         <f t="shared" ref="C18:D18" si="1">C16*C17</f>
         <v>200</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="17">
         <f t="shared" si="1"/>
         <v>560</v>
       </c>
     </row>
-    <row r="19" spans="1:4" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="20"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
@@ -5709,13 +11303,13 @@
       <c r="A21" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="21">
+      <c r="B21" s="18">
         <v>0</v>
       </c>
-      <c r="C21" s="21">
+      <c r="C21" s="18">
         <v>50</v>
       </c>
-      <c r="D21" s="21">
+      <c r="D21" s="18">
         <v>50</v>
       </c>
     </row>
@@ -5751,15 +11345,15 @@
       <c r="A24" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B24" s="21">
+      <c r="B24" s="18">
         <f>B22*B21*B23</f>
         <v>0</v>
       </c>
-      <c r="C24" s="21">
+      <c r="C24" s="18">
         <f t="shared" ref="C24" si="2">C22*C21*C23</f>
         <v>400</v>
       </c>
-      <c r="D24" s="21">
+      <c r="D24" s="18">
         <f t="shared" ref="D24" si="3">D22*D21*D23</f>
         <v>400</v>
       </c>
@@ -5772,7 +11366,7 @@
       <c r="C26" s="13"/>
       <c r="D26" s="13"/>
     </row>
-    <row r="27" spans="1:4" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>42</v>
       </c>
@@ -5860,8 +11454,8 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="34" spans="1:4" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="22" t="s">
+    <row r="34" spans="1:4" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="19" t="s">
         <v>20</v>
       </c>
     </row>
@@ -6009,13 +11603,13 @@
       <c r="A45" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B45" s="17">
+      <c r="B45" s="16">
         <v>4</v>
       </c>
-      <c r="C45" s="17">
+      <c r="C45" s="16">
         <v>4</v>
       </c>
-      <c r="D45" s="17">
+      <c r="D45" s="16">
         <v>4</v>
       </c>
     </row>
@@ -6023,15 +11617,15 @@
       <c r="A46" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B46" s="18">
+      <c r="B46" s="4">
         <f>(SUM(B36:B44) *B45)</f>
         <v>2200</v>
       </c>
-      <c r="C46" s="18">
+      <c r="C46" s="4">
         <f t="shared" ref="C46" si="5">(SUM(C36:C44) *C45)</f>
         <v>1456</v>
       </c>
-      <c r="D46" s="18">
+      <c r="D46" s="4">
         <f t="shared" ref="D46" si="6">(SUM(D36:D44) *D45)</f>
         <v>268</v>
       </c>
@@ -6076,15 +11670,15 @@
       <c r="A51" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B51" s="19">
+      <c r="B51" s="17">
         <f>B49*B50</f>
         <v>1400</v>
       </c>
-      <c r="C51" s="19">
+      <c r="C51" s="17">
         <f t="shared" ref="C51" si="7">C49*C50</f>
         <v>400</v>
       </c>
-      <c r="D51" s="19">
+      <c r="D51" s="17">
         <f t="shared" ref="D51" si="8">D49*D50</f>
         <v>1120</v>
       </c>
@@ -6101,13 +11695,13 @@
       <c r="A54" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B54" s="21">
+      <c r="B54" s="18">
         <v>0</v>
       </c>
-      <c r="C54" s="21">
+      <c r="C54" s="18">
         <v>50</v>
       </c>
-      <c r="D54" s="21">
+      <c r="D54" s="18">
         <v>50</v>
       </c>
     </row>
@@ -6143,15 +11737,15 @@
       <c r="A57" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B57" s="21">
+      <c r="B57" s="18">
         <f>B55*B54*B56</f>
         <v>0</v>
       </c>
-      <c r="C57" s="21">
+      <c r="C57" s="18">
         <f t="shared" ref="C57:D57" si="9">C55*C54*C56</f>
         <v>800</v>
       </c>
-      <c r="D57" s="21">
+      <c r="D57" s="18">
         <f t="shared" si="9"/>
         <v>800</v>
       </c>
@@ -6294,4 +11888,1715 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE8BDDD1-C73D-4B8F-B476-C89108ABFAA7}">
+  <dimension ref="A1:D41"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="21"/>
+      <c r="B2" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3" s="22">
+        <v>29</v>
+      </c>
+      <c r="C3" s="22">
+        <v>149</v>
+      </c>
+      <c r="D3" s="22">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5" s="23">
+        <v>40</v>
+      </c>
+      <c r="C5" s="23">
+        <v>90</v>
+      </c>
+      <c r="D5" s="23">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="24">
+        <v>200</v>
+      </c>
+      <c r="C6" s="24">
+        <v>1000</v>
+      </c>
+      <c r="D6" s="24">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="23">
+        <f>B5/B6</f>
+        <v>0.2</v>
+      </c>
+      <c r="C7" s="23">
+        <f t="shared" ref="C7:D7" si="0">C5/C6</f>
+        <v>0.09</v>
+      </c>
+      <c r="D7" s="23">
+        <f t="shared" si="0"/>
+        <v>3.3636363636363638E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" s="25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" s="10">
+        <f>B11*B10*B9</f>
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="26">
+        <f>$B$12</f>
+        <v>3900</v>
+      </c>
+      <c r="C14" s="26">
+        <f t="shared" ref="C14:D14" si="1">$B$12</f>
+        <v>3900</v>
+      </c>
+      <c r="D14" s="26">
+        <f t="shared" si="1"/>
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="B15" s="27">
+        <f>B14*B7</f>
+        <v>780</v>
+      </c>
+      <c r="C15" s="27">
+        <f t="shared" ref="C15:D15" si="2">C14*C7</f>
+        <v>351</v>
+      </c>
+      <c r="D15" s="27">
+        <f t="shared" si="2"/>
+        <v>131.18181818181819</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="B16" s="26">
+        <v>2</v>
+      </c>
+      <c r="C16" s="26">
+        <v>2</v>
+      </c>
+      <c r="D16" s="26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" s="28"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="29">
+        <f>SUM(B3,B16*B15)</f>
+        <v>1589</v>
+      </c>
+      <c r="C20" s="29">
+        <f t="shared" ref="C20:D20" si="3">SUM(C3,C16*C15)</f>
+        <v>851</v>
+      </c>
+      <c r="D20" s="29">
+        <f t="shared" si="3"/>
+        <v>811.36363636363637</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="21"/>
+      <c r="B23" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" s="22">
+        <v>29</v>
+      </c>
+      <c r="C24" s="22">
+        <v>149</v>
+      </c>
+      <c r="D24" s="22">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="20"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B26" s="23">
+        <v>40</v>
+      </c>
+      <c r="C26" s="23">
+        <v>90</v>
+      </c>
+      <c r="D26" s="23">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B27" s="24">
+        <v>200</v>
+      </c>
+      <c r="C27" s="24">
+        <v>1000</v>
+      </c>
+      <c r="D27" s="24">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B28" s="23">
+        <f>B26/B27</f>
+        <v>0.2</v>
+      </c>
+      <c r="C28" s="23">
+        <f t="shared" ref="C28" si="4">C26/C27</f>
+        <v>0.09</v>
+      </c>
+      <c r="D28" s="23">
+        <f t="shared" ref="D28" si="5">D26/D27</f>
+        <v>3.3636363636363638E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B30" s="10">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" s="25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" s="25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B33" s="10">
+        <f>B32*B31*B30</f>
+        <v>130000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="B35" s="26">
+        <f>$B$33</f>
+        <v>130000</v>
+      </c>
+      <c r="C35" s="26">
+        <f t="shared" ref="C35:D35" si="6">$B$33</f>
+        <v>130000</v>
+      </c>
+      <c r="D35" s="26">
+        <f t="shared" si="6"/>
+        <v>130000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="B36" s="27">
+        <f>B35*B28</f>
+        <v>26000</v>
+      </c>
+      <c r="C36" s="27">
+        <f t="shared" ref="C36" si="7">C35*C28</f>
+        <v>11700</v>
+      </c>
+      <c r="D36" s="27">
+        <f t="shared" ref="D36" si="8">D35*D28</f>
+        <v>4372.727272727273</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="B37" s="26">
+        <v>2</v>
+      </c>
+      <c r="C37" s="26">
+        <v>2</v>
+      </c>
+      <c r="D37" s="26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B39" s="28"/>
+      <c r="C39" s="28"/>
+      <c r="D39" s="28"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B41" s="29">
+        <f>SUM(B24,B37*B36)</f>
+        <v>52029</v>
+      </c>
+      <c r="C41" s="29">
+        <f t="shared" ref="C41:D41" si="9">SUM(C24,C37*C36)</f>
+        <v>23549</v>
+      </c>
+      <c r="D41" s="29">
+        <f t="shared" si="9"/>
+        <v>9294.454545454546</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B20:D20">
+    <cfRule type="iconSet" priority="4">
+      <iconSet iconSet="3Symbols" reverse="1">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B41:D41">
+    <cfRule type="iconSet" priority="1">
+      <iconSet iconSet="3Symbols" reverse="1">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD452E1B-1879-4CF0-996C-9C35CD60B3B3}">
+  <dimension ref="A1:D35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="3">
+        <v>19</v>
+      </c>
+      <c r="C3" s="3">
+        <v>35</v>
+      </c>
+      <c r="D3" s="3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" s="13">
+        <v>1</v>
+      </c>
+      <c r="C4" s="13">
+        <v>1</v>
+      </c>
+      <c r="D4" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="3">
+        <v>20</v>
+      </c>
+      <c r="C5" s="3">
+        <v>15</v>
+      </c>
+      <c r="D5" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="B6" s="13">
+        <v>2</v>
+      </c>
+      <c r="C6" s="13">
+        <v>2</v>
+      </c>
+      <c r="D6" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" s="30">
+        <v>24</v>
+      </c>
+      <c r="C7" s="30">
+        <v>24</v>
+      </c>
+      <c r="D7" s="30">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="3">
+        <f t="shared" ref="B8:C8" si="0">SUM(B3,B5*B6)*B7</f>
+        <v>1416</v>
+      </c>
+      <c r="C8" s="3">
+        <f t="shared" si="0"/>
+        <v>1560</v>
+      </c>
+      <c r="D8" s="3">
+        <f>SUM(D3,D5*D6)*D7</f>
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B10" s="12">
+        <v>0</v>
+      </c>
+      <c r="C10" s="12">
+        <v>500</v>
+      </c>
+      <c r="D10" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" s="12">
+        <v>30</v>
+      </c>
+      <c r="C11" s="12">
+        <v>0</v>
+      </c>
+      <c r="D11" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" s="9">
+        <v>24</v>
+      </c>
+      <c r="C12" s="9">
+        <v>0</v>
+      </c>
+      <c r="D12" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="12">
+        <f>SUM(B12*B11, B10)</f>
+        <v>720</v>
+      </c>
+      <c r="C13" s="12">
+        <f t="shared" ref="C13:D13" si="1">SUM(C12*C11, C10)</f>
+        <v>500</v>
+      </c>
+      <c r="D13" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="32"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
+    </row>
+    <row r="15" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="15">
+        <f>SUM(B13,B8)</f>
+        <v>2136</v>
+      </c>
+      <c r="C17" s="15">
+        <f t="shared" ref="C17:D17" si="2">SUM(C13,C8)</f>
+        <v>2060</v>
+      </c>
+      <c r="D17" s="15">
+        <f t="shared" si="2"/>
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" s="33" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="34" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="13"/>
+      <c r="B20" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B21" s="3">
+        <v>19</v>
+      </c>
+      <c r="C21" s="3">
+        <v>35</v>
+      </c>
+      <c r="D21" s="3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B22" s="13">
+        <v>1</v>
+      </c>
+      <c r="C22" s="13">
+        <v>1</v>
+      </c>
+      <c r="D22" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B23" s="3">
+        <v>20</v>
+      </c>
+      <c r="C23" s="3">
+        <v>15</v>
+      </c>
+      <c r="D23" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="B24" s="13">
+        <v>0</v>
+      </c>
+      <c r="C24" s="13">
+        <v>0</v>
+      </c>
+      <c r="D24" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="B25" s="30">
+        <v>24</v>
+      </c>
+      <c r="C25" s="30">
+        <v>24</v>
+      </c>
+      <c r="D25" s="30">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26" s="3">
+        <f t="shared" ref="B26" si="3">SUM(B21,B23*B24)*B25</f>
+        <v>456</v>
+      </c>
+      <c r="C26" s="3">
+        <f t="shared" ref="C26" si="4">SUM(C21,C23*C24)*C25</f>
+        <v>840</v>
+      </c>
+      <c r="D26" s="3">
+        <f>SUM(D21,D23*D24)*D25</f>
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" s="12">
+        <v>0</v>
+      </c>
+      <c r="C28" s="12">
+        <v>500</v>
+      </c>
+      <c r="D28" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B29" s="12">
+        <v>30</v>
+      </c>
+      <c r="C29" s="12">
+        <v>0</v>
+      </c>
+      <c r="D29" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B30" s="9">
+        <v>24</v>
+      </c>
+      <c r="C30" s="9">
+        <v>0</v>
+      </c>
+      <c r="D30" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31" s="12">
+        <f>SUM(B30*B29, B28)</f>
+        <v>720</v>
+      </c>
+      <c r="C31" s="12">
+        <f t="shared" ref="C31" si="5">SUM(C30*C29, C28)</f>
+        <v>500</v>
+      </c>
+      <c r="D31" s="12">
+        <f t="shared" ref="D31" si="6">SUM(D30*D29, D28)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="31"/>
+      <c r="B32" s="32"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="32"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="15">
+        <f>SUM(B31,B26)</f>
+        <v>1176</v>
+      </c>
+      <c r="C35" s="15">
+        <f t="shared" ref="C35:D35" si="7">SUM(C31,C26)</f>
+        <v>1340</v>
+      </c>
+      <c r="D35" s="15">
+        <f t="shared" si="7"/>
+        <v>1320</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B17:D17">
+    <cfRule type="iconSet" priority="2">
+      <iconSet iconSet="3Symbols" reverse="1">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
+    <cfRule type="iconSet" priority="7">
+      <iconSet iconSet="3Symbols">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35:D35">
+    <cfRule type="iconSet" priority="1">
+      <iconSet iconSet="3Symbols" reverse="1">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
+    <cfRule type="iconSet" priority="4">
+      <iconSet iconSet="3Symbols">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03ED0A0D-A694-4047-BDF8-609B2275C7F4}">
+  <dimension ref="A1:E63"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="21"/>
+      <c r="B3" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="B4" s="35">
+        <v>14500</v>
+      </c>
+      <c r="C4" s="35">
+        <v>31000</v>
+      </c>
+      <c r="D4" s="35">
+        <v>72000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="B5" s="35">
+        <v>1450</v>
+      </c>
+      <c r="C5" s="35">
+        <v>3100</v>
+      </c>
+      <c r="D5" s="35">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" s="35">
+        <f>SUM(B5,B4)</f>
+        <v>15950</v>
+      </c>
+      <c r="C6" s="35">
+        <f t="shared" ref="C6:D6" si="0">SUM(C5,C4)</f>
+        <v>34100</v>
+      </c>
+      <c r="D6" s="35">
+        <f t="shared" si="0"/>
+        <v>79200</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" s="31" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="32"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="B9" s="36">
+        <v>0</v>
+      </c>
+      <c r="C9" s="36">
+        <v>0</v>
+      </c>
+      <c r="D9" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="B10" s="4">
+        <f>B9*B4</f>
+        <v>0</v>
+      </c>
+      <c r="C10" s="4">
+        <f t="shared" ref="C10:D10" si="1">C9*C4</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="B13" s="9">
+        <v>90</v>
+      </c>
+      <c r="C13" s="9">
+        <v>390</v>
+      </c>
+      <c r="D13" s="9">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B14" s="9">
+        <v>35</v>
+      </c>
+      <c r="C14" s="9">
+        <v>19</v>
+      </c>
+      <c r="D14" s="9">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B15" s="12">
+        <v>5.35</v>
+      </c>
+      <c r="C15" s="12">
+        <v>5.35</v>
+      </c>
+      <c r="D15" s="12">
+        <v>5.35</v>
+      </c>
+      <c r="E15" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="B16" s="12">
+        <f>(B26/B14)*B15</f>
+        <v>4585.7142857142853</v>
+      </c>
+      <c r="C16" s="12">
+        <f t="shared" ref="C16:D16" si="2">(C26/C14)*C15</f>
+        <v>8447.3684210526317</v>
+      </c>
+      <c r="D16" s="12">
+        <f t="shared" si="2"/>
+        <v>9441.1764705882342</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B19" s="11">
+        <v>1500</v>
+      </c>
+      <c r="C19" s="11">
+        <v>2500</v>
+      </c>
+      <c r="D19" s="11">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B20" s="11">
+        <v>210</v>
+      </c>
+      <c r="C20" s="11">
+        <v>300</v>
+      </c>
+      <c r="D20" s="11">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="B21" s="11">
+        <f>B16</f>
+        <v>4585.7142857142853</v>
+      </c>
+      <c r="C21" s="11">
+        <f t="shared" ref="C21:D21" si="3">C16</f>
+        <v>8447.3684210526317</v>
+      </c>
+      <c r="D21" s="11">
+        <f t="shared" si="3"/>
+        <v>9441.1764705882342</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="11">
+        <f>SUM(B21,B20,B19)</f>
+        <v>6295.7142857142853</v>
+      </c>
+      <c r="C22" s="11">
+        <f t="shared" ref="C22:D22" si="4">SUM(C21,C20,C19)</f>
+        <v>11247.368421052632</v>
+      </c>
+      <c r="D22" s="11">
+        <f t="shared" si="4"/>
+        <v>12991.176470588234</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="32"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="B25" s="26">
+        <v>250000</v>
+      </c>
+      <c r="C25" s="26">
+        <v>250000</v>
+      </c>
+      <c r="D25" s="26">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="B26" s="26">
+        <v>30000</v>
+      </c>
+      <c r="C26" s="26">
+        <v>30000</v>
+      </c>
+      <c r="D26" s="26">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="B27" s="37">
+        <f>B25/B26</f>
+        <v>8.3333333333333339</v>
+      </c>
+      <c r="C27" s="37">
+        <f t="shared" ref="C27:D27" si="5">C25/C26</f>
+        <v>8.3333333333333339</v>
+      </c>
+      <c r="D27" s="37">
+        <f t="shared" si="5"/>
+        <v>8.3333333333333339</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31" s="15">
+        <f>(B27*B22)+B6+B10</f>
+        <v>68414.28571428571</v>
+      </c>
+      <c r="C31" s="15">
+        <f t="shared" ref="C31:D31" si="6">(C27*C22)+C6+C10</f>
+        <v>127828.07017543861</v>
+      </c>
+      <c r="D31" s="15">
+        <f t="shared" si="6"/>
+        <v>187459.80392156861</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="21"/>
+      <c r="B35" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="C35" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="D35" s="21" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="B36" s="35">
+        <v>14500</v>
+      </c>
+      <c r="C36" s="35">
+        <v>31000</v>
+      </c>
+      <c r="D36" s="35">
+        <v>72000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="B37" s="35">
+        <v>1450</v>
+      </c>
+      <c r="C37" s="35">
+        <v>3100</v>
+      </c>
+      <c r="D37" s="35">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="B38" s="35">
+        <f>SUM(B37,B36)</f>
+        <v>15950</v>
+      </c>
+      <c r="C38" s="35">
+        <f t="shared" ref="C38" si="7">SUM(C37,C36)</f>
+        <v>34100</v>
+      </c>
+      <c r="D38" s="35">
+        <f t="shared" ref="D38" si="8">SUM(D37,D36)</f>
+        <v>79200</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="31"/>
+      <c r="B39" s="32"/>
+      <c r="C39" s="32"/>
+      <c r="D39" s="32"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="B41" s="36">
+        <v>0.4</v>
+      </c>
+      <c r="C41" s="36">
+        <v>0.4</v>
+      </c>
+      <c r="D41" s="36">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="B42" s="4">
+        <f>B41*B36</f>
+        <v>5800</v>
+      </c>
+      <c r="C42" s="4">
+        <f t="shared" ref="C42:D42" si="9">C41*C36</f>
+        <v>12400</v>
+      </c>
+      <c r="D42" s="4">
+        <f t="shared" si="9"/>
+        <v>28800</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="B44" s="13"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="13"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="B45" s="9">
+        <v>90</v>
+      </c>
+      <c r="C45" s="9">
+        <v>390</v>
+      </c>
+      <c r="D45" s="9">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B46" s="9">
+        <v>35</v>
+      </c>
+      <c r="C46" s="9">
+        <v>19</v>
+      </c>
+      <c r="D46" s="9">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B47" s="12">
+        <v>5.35</v>
+      </c>
+      <c r="C47" s="12">
+        <v>5.35</v>
+      </c>
+      <c r="D47" s="12">
+        <v>5.35</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="B48" s="12">
+        <f>(B58/B46)*B47</f>
+        <v>4585.7142857142853</v>
+      </c>
+      <c r="C48" s="12">
+        <f t="shared" ref="C48" si="10">(C58/C46)*C47</f>
+        <v>8447.3684210526317</v>
+      </c>
+      <c r="D48" s="12">
+        <f t="shared" ref="D48" si="11">(D58/D46)*D47</f>
+        <v>9441.1764705882342</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B50" s="13"/>
+      <c r="C50" s="13"/>
+      <c r="D50" s="13"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B51" s="11">
+        <v>1500</v>
+      </c>
+      <c r="C51" s="11">
+        <v>2500</v>
+      </c>
+      <c r="D51" s="11">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B52" s="11">
+        <v>210</v>
+      </c>
+      <c r="C52" s="11">
+        <v>300</v>
+      </c>
+      <c r="D52" s="11">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="B53" s="11">
+        <f>B48</f>
+        <v>4585.7142857142853</v>
+      </c>
+      <c r="C53" s="11">
+        <f t="shared" ref="C53:D53" si="12">C48</f>
+        <v>8447.3684210526317</v>
+      </c>
+      <c r="D53" s="11">
+        <f t="shared" si="12"/>
+        <v>9441.1764705882342</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B54" s="11">
+        <f>SUM(B53,B52,B51)</f>
+        <v>6295.7142857142853</v>
+      </c>
+      <c r="C54" s="11">
+        <f t="shared" ref="C54" si="13">SUM(C53,C52,C51)</f>
+        <v>11247.368421052632</v>
+      </c>
+      <c r="D54" s="11">
+        <f t="shared" ref="D54" si="14">SUM(D53,D52,D51)</f>
+        <v>12991.176470588234</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="31"/>
+      <c r="B55" s="32"/>
+      <c r="C55" s="32"/>
+      <c r="D55" s="32"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B56" s="13"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="13"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="B57" s="26">
+        <v>250000</v>
+      </c>
+      <c r="C57" s="26">
+        <v>250000</v>
+      </c>
+      <c r="D57" s="26">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="B58" s="26">
+        <v>30000</v>
+      </c>
+      <c r="C58" s="26">
+        <v>30000</v>
+      </c>
+      <c r="D58" s="26">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="B59" s="37">
+        <f>B57/B58</f>
+        <v>8.3333333333333339</v>
+      </c>
+      <c r="C59" s="37">
+        <f t="shared" ref="C59" si="15">C57/C58</f>
+        <v>8.3333333333333339</v>
+      </c>
+      <c r="D59" s="37">
+        <f t="shared" ref="D59" si="16">D57/D58</f>
+        <v>8.3333333333333339</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="B61" s="13"/>
+      <c r="C61" s="13"/>
+      <c r="D61" s="13"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="1"/>
+      <c r="B62" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B63" s="15">
+        <f>(B59*B54)+B38+B42</f>
+        <v>74214.28571428571</v>
+      </c>
+      <c r="C63" s="15">
+        <f t="shared" ref="C63:D63" si="17">(C59*C54)+C38+C42</f>
+        <v>140228.0701754386</v>
+      </c>
+      <c r="D63" s="15">
+        <f t="shared" si="17"/>
+        <v>216259.80392156861</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B31:D31">
+    <cfRule type="iconSet" priority="4">
+      <iconSet iconSet="3Symbols" reverse="1">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
+    <cfRule type="iconSet" priority="6">
+      <iconSet iconSet="3Symbols">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B63:D63">
+    <cfRule type="iconSet" priority="1">
+      <iconSet iconSet="3Symbols" reverse="1">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
+    <cfRule type="iconSet" priority="2">
+      <iconSet iconSet="3Symbols">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>